--- a/exports/RECLTD_full_report.xlsx
+++ b/exports/RECLTD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>4.17</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.38541666666</v>
+        <v>44582.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>101.8</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>101.3526422549143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.54</v>
+        <v>-4.4</v>
       </c>
       <c r="L2" t="n">
-        <v>3.16</v>
+        <v>5.12</v>
       </c>
       <c r="M2" t="n">
         <v>0.24</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.42</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>101.1</v>
+        <v>103.2</v>
       </c>
       <c r="I3" t="n">
         <v>102.1537491498706</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.25</v>
+        <v>-3.36</v>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>3.61</v>
       </c>
       <c r="M3" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>2.48</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>5.94</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44606.38541666666</v>
+        <v>44606.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>101.9</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>100.7428805559463</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.26</v>
+        <v>-3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>6.74</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44642.55208333334</v>
+        <v>44643.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>94.25</v>
+        <v>94.75</v>
       </c>
       <c r="I5" t="n">
         <v>94.603502795249</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>5.61</v>
+        <v>5.11</v>
       </c>
       <c r="L5" t="n">
         <v>2.15</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>4.41</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>96.45</v>
+        <v>94.75</v>
       </c>
       <c r="I6" t="n">
         <v>96.19734754167582</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>3.48</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>4.87</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.38541666666</v>
+        <v>44735.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>86.8</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="I7" t="n">
         <v>87.50879222553671</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>8.390000000000001</v>
+        <v>7.28</v>
       </c>
       <c r="L7" t="n">
         <v>2.69</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>5.75</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44753.55208333334</v>
+        <v>44754.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>97.95</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>94.07740551791919</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>11.5</v>
+        <v>6.32</v>
       </c>
       <c r="L8" t="n">
         <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8100000000000001</v>
+        <v>3.93</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>4.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.56</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.53</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44764.55208333334</v>
+        <v>44767.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>94.5</v>
+        <v>95.95</v>
       </c>
       <c r="I9" t="n">
         <v>94.79314169027144</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.18</v>
+        <v>-2.73</v>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>2.84</v>
       </c>
       <c r="M9" t="n">
         <v>1.01</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>4.28</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>106.4</v>
+        <v>103.65</v>
       </c>
       <c r="I10" t="n">
         <v>104.9241359463659</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K10" t="n">
-        <v>10.89</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>1.25</v>
@@ -1011,7 +1130,7 @@
         <v>2.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
         <v>1.75</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>6.14</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44855.55208333334</v>
+        <v>44858.76041666666</v>
       </c>
       <c r="H11" t="n">
-        <v>93.55</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>94.80852594188585</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38.375</v>
       </c>
       <c r="K11" t="n">
-        <v>9.74</v>
+        <v>8.44</v>
       </c>
       <c r="L11" t="n">
         <v>3.81</v>
       </c>
       <c r="M11" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="N11" t="n">
         <v>2.84</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>3.61</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>100.6</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>100.469233511638</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>15.79166666666667</v>
+        <v>16.625</v>
       </c>
       <c r="K12" t="n">
-        <v>6.01</v>
+        <v>5.22</v>
       </c>
       <c r="L12" t="n">
         <v>1.84</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>3.97</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44888.55208333334</v>
+        <v>44889.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>99.55</v>
+        <v>102.95</v>
       </c>
       <c r="I13" t="n">
         <v>102.6095735487954</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3</v>
+        <v>-3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>3.66</v>
       </c>
       <c r="M13" t="n">
         <v>0.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.55</v>
+        <v>3.62</v>
       </c>
       <c r="O13" t="n">
         <v>-1.09</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.03</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44918.38541666666</v>
+        <v>44918.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>109.75</v>
+        <v>109</v>
       </c>
       <c r="I14" t="n">
         <v>109.5300348884355</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>6.61</v>
+        <v>5.88</v>
       </c>
       <c r="L14" t="n">
         <v>3.11</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>5.75</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>113.95</v>
+        <v>117.1</v>
       </c>
       <c r="I15" t="n">
         <v>115.2704980536852</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.54</v>
+        <v>-7.43</v>
       </c>
       <c r="L15" t="n">
-        <v>5.87</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>0.53</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.86</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>120.9</v>
+        <v>114.35</v>
       </c>
       <c r="I16" t="n">
         <v>119.6734095982852</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>-2.35</v>
       </c>
       <c r="L16" t="n">
-        <v>2.99</v>
+        <v>4.27</v>
       </c>
       <c r="M16" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>4.59</v>
       </c>
       <c r="O16" t="n">
         <v>2.37</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.140000000000001</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>115.75</v>
+        <v>118.4</v>
       </c>
       <c r="I17" t="n">
         <v>116.2296464754471</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.22</v>
+        <v>-3.54</v>
       </c>
       <c r="L17" t="n">
         <v>7.87</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.56</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>120.6</v>
+        <v>120.15</v>
       </c>
       <c r="I18" t="n">
         <v>120.5630060625398</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="L18" t="n">
         <v>1.6</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>5.36</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>117.7</v>
+        <v>119.4</v>
       </c>
       <c r="I19" t="n">
         <v>118.9461305813172</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>2.04</v>
+        <v>0.62</v>
       </c>
       <c r="L19" t="n">
         <v>0.71</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.21</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45064.38541666666</v>
+        <v>45064.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>131.6</v>
+        <v>129.25</v>
       </c>
       <c r="I20" t="n">
         <v>131.1415447822185</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>10.22</v>
+        <v>8.25</v>
       </c>
       <c r="L20" t="n">
         <v>2.26</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>6.74</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>133.45</v>
+        <v>136.2</v>
       </c>
       <c r="I21" t="n">
         <v>136.1389109465673</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.25</v>
+        <v>-5.38</v>
       </c>
       <c r="L21" t="n">
-        <v>3.56</v>
+        <v>6.62</v>
       </c>
       <c r="M21" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="N21" t="n">
         <v>1.8</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>4.88</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45120.55208333334</v>
+        <v>45121.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>165.6</v>
+        <v>160.35</v>
       </c>
       <c r="I22" t="n">
         <v>161.5169158543419</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K22" t="n">
-        <v>21.59</v>
+        <v>17.73</v>
       </c>
       <c r="L22" t="n">
         <v>1.62</v>
       </c>
       <c r="M22" t="n">
-        <v>0.14</v>
+        <v>2.29</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.94</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45128.55208333334</v>
+        <v>45131.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>161.8</v>
+        <v>175.35</v>
       </c>
       <c r="I23" t="n">
         <v>167.4651071716267</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.9</v>
+        <v>-9.35</v>
       </c>
       <c r="L23" t="n">
-        <v>1.84</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.34</v>
+        <v>0.8</v>
       </c>
       <c r="N23" t="n">
-        <v>1.44</v>
+        <v>6.83</v>
       </c>
       <c r="O23" t="n">
         <v>-3.2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.19</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>270.8</v>
+        <v>251.05</v>
       </c>
       <c r="I24" t="n">
         <v>253.9017985398551</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K24" t="n">
-        <v>54.43</v>
+        <v>43.17</v>
       </c>
       <c r="L24" t="n">
         <v>7.41</v>
@@ -1809,7 +2096,7 @@
         <v>1.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3.17</v>
+        <v>8.42</v>
       </c>
       <c r="O24" t="n">
         <v>6.83</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>14.58</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45191.55208333334</v>
+        <v>45194.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>270.45</v>
+        <v>272.15</v>
       </c>
       <c r="I25" t="n">
         <v>270.6435839407039</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.73</v>
+        <v>-8.4</v>
       </c>
       <c r="L25" t="n">
-        <v>8.52</v>
+        <v>8.9</v>
       </c>
       <c r="M25" t="n">
         <v>1.1</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>287.6</v>
+        <v>276.15</v>
       </c>
       <c r="I26" t="n">
         <v>280.2367641411835</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
-        <v>5.68</v>
+        <v>1.47</v>
       </c>
       <c r="L26" t="n">
         <v>2.37</v>
@@ -1923,7 +2234,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.78</v>
+        <v>3.27</v>
       </c>
       <c r="O26" t="n">
         <v>0.09</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45230.38541666666</v>
+        <v>45230.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>280.75</v>
+        <v>288</v>
       </c>
       <c r="I27" t="n">
         <v>287.0027716980409</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.67</v>
+        <v>-4.29</v>
       </c>
       <c r="L27" t="n">
         <v>5.43</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>430.8</v>
+        <v>402.55</v>
       </c>
       <c r="I28" t="n">
         <v>408.1638337414911</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>49.83333333333334</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>49.58</v>
+        <v>39.77</v>
       </c>
       <c r="L28" t="n">
         <v>5.16</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>13.46</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45309.55208333334</v>
+        <v>45310.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>428</v>
+        <v>451.45</v>
       </c>
       <c r="I29" t="n">
         <v>440.3426390690317</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-6.32</v>
+        <v>-12.15</v>
       </c>
       <c r="L29" t="n">
-        <v>11.24</v>
+        <v>12.62</v>
       </c>
       <c r="M29" t="n">
-        <v>0.92</v>
+        <v>1.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.04</v>
+        <v>5.84</v>
       </c>
       <c r="O29" t="n">
         <v>-7.67</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>483.5</v>
+        <v>462.55</v>
       </c>
       <c r="I30" t="n">
         <v>472.3331310892513</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K30" t="n">
-        <v>7.1</v>
+        <v>2.46</v>
       </c>
       <c r="L30" t="n">
         <v>7.81</v>
@@ -2151,7 +2510,7 @@
         <v>1.28</v>
       </c>
       <c r="N30" t="n">
-        <v>5.1</v>
+        <v>6.19</v>
       </c>
       <c r="O30" t="n">
         <v>5.84</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>13.56</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>456.3</v>
+        <v>467.3</v>
       </c>
       <c r="I31" t="n">
         <v>463.9620447586033</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K31" t="n">
-        <v>1.35</v>
+        <v>-1.03</v>
       </c>
       <c r="L31" t="n">
         <v>5.8</v>
       </c>
       <c r="M31" t="n">
-        <v>0.64</v>
+        <v>1.86</v>
       </c>
       <c r="N31" t="n">
         <v>3.87</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>460.3</v>
+        <v>447.65</v>
       </c>
       <c r="I32" t="n">
         <v>452.5857706515802</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.5</v>
+        <v>-4.21</v>
       </c>
       <c r="L32" t="n">
-        <v>3.78</v>
+        <v>5.52</v>
       </c>
       <c r="M32" t="n">
         <v>0.02</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45384.55208333334</v>
+        <v>45385.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>463.5</v>
+        <v>471.6</v>
       </c>
       <c r="I33" t="n">
         <v>466.9086190171413</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.54</v>
+        <v>-5.35</v>
       </c>
       <c r="L33" t="n">
-        <v>4.62</v>
+        <v>6.09</v>
       </c>
       <c r="M33" t="n">
         <v>1.53</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>8.17</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45390.55208333334</v>
+        <v>45391.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>453.8</v>
+        <v>441.85</v>
       </c>
       <c r="I34" t="n">
         <v>444.1937573816049</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>-3.77</v>
+        <v>-6.31</v>
       </c>
       <c r="L34" t="n">
-        <v>4.03</v>
+        <v>6.66</v>
       </c>
       <c r="M34" t="n">
         <v>0.96</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.09</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>452.45</v>
+        <v>460.5</v>
       </c>
       <c r="I35" t="n">
         <v>453.7466756717371</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.4</v>
+        <v>-4.22</v>
       </c>
       <c r="L35" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="M35" t="n">
         <v>0.93</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.58</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>558.9</v>
+        <v>513.1</v>
       </c>
       <c r="I36" t="n">
         <v>514.8421150109851</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>21.37</v>
+        <v>11.42</v>
       </c>
       <c r="L36" t="n">
         <v>1.78</v>
       </c>
       <c r="M36" t="n">
-        <v>-0</v>
+        <v>4.99</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>7.64</v>
       </c>
       <c r="O36" t="n">
         <v>1.12</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>11.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45436.55208333334</v>
+        <v>45439.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>554.75</v>
+        <v>565.4</v>
       </c>
       <c r="I37" t="n">
         <v>562.5712870071634</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.119999999999999</v>
+        <v>-10.19</v>
       </c>
       <c r="L37" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="M37" t="n">
         <v>1.42</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.96</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45442.55208333334</v>
+        <v>45443.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>550</v>
+        <v>532.25</v>
       </c>
       <c r="I38" t="n">
         <v>536.4242944424496</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.72</v>
+        <v>-5.86</v>
       </c>
       <c r="L38" t="n">
-        <v>3.61</v>
+        <v>7.04</v>
       </c>
       <c r="M38" t="n">
         <v>0.78</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>10.89</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>538</v>
+        <v>603.85</v>
       </c>
       <c r="I39" t="n">
         <v>583.5754344941402</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.08</v>
+        <v>-13.45</v>
       </c>
       <c r="L39" t="n">
-        <v>4.82</v>
+        <v>13.69</v>
       </c>
       <c r="M39" t="n">
-        <v>0.93</v>
+        <v>7.43</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>12.54</v>
       </c>
       <c r="O39" t="n">
         <v>-2.18</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.11</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>605.45</v>
+        <v>485.3</v>
       </c>
       <c r="I40" t="n">
         <v>545.8156480597464</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.26</v>
+        <v>-19.63</v>
       </c>
       <c r="L40" t="n">
-        <v>5.85</v>
+        <v>25.4</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>24.19</v>
       </c>
       <c r="O40" t="n">
         <v>12.54</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>27.99</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45474.38541666666</v>
+        <v>45474.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>547.85</v>
+        <v>551</v>
       </c>
       <c r="I41" t="n">
         <v>549.2512796896114</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-12.89</v>
+        <v>-13.54</v>
       </c>
       <c r="L41" t="n">
         <v>22.4</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.82</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>611</v>
+        <v>602.55</v>
       </c>
       <c r="I42" t="n">
         <v>602.6552599540778</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>10.89</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L42" t="n">
         <v>3.72</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45530.55208333334</v>
+        <v>45531.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>589.9</v>
+        <v>605.1</v>
       </c>
       <c r="I43" t="n">
         <v>599.2729925449045</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K43" t="n">
-        <v>2.1</v>
+        <v>-0.42</v>
       </c>
       <c r="L43" t="n">
         <v>7.97</v>
@@ -2892,7 +3407,7 @@
         <v>2.76</v>
       </c>
       <c r="N43" t="n">
-        <v>4.03</v>
+        <v>4.47</v>
       </c>
       <c r="O43" t="n">
         <v>-2.05</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>6.3</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>607</v>
+        <v>582.6</v>
       </c>
       <c r="I44" t="n">
         <v>603.3194284255183</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K44" t="n">
-        <v>0.31</v>
+        <v>-3.72</v>
       </c>
       <c r="L44" t="n">
-        <v>3.07</v>
+        <v>4.06</v>
       </c>
       <c r="M44" t="n">
         <v>1.54</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.15</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45574.55208333334</v>
+        <v>45575.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>532</v>
+        <v>543.4</v>
       </c>
       <c r="I45" t="n">
         <v>538.1127656053641</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>8.69</v>
+        <v>6.73</v>
       </c>
       <c r="L45" t="n">
         <v>4.02</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>528.85</v>
+        <v>515.75</v>
       </c>
       <c r="I46" t="n">
         <v>523.5705136946691</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.68</v>
+        <v>-5.09</v>
       </c>
       <c r="L46" t="n">
-        <v>2.68</v>
+        <v>5.53</v>
       </c>
       <c r="M46" t="n">
         <v>0.64</v>
       </c>
       <c r="N46" t="n">
-        <v>2.93</v>
+        <v>3.66</v>
       </c>
       <c r="O46" t="n">
         <v>2.16</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45594.38541666666</v>
+        <v>45594.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>529.75</v>
+        <v>548.55</v>
       </c>
       <c r="I47" t="n">
         <v>542.1627260981051</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.71</v>
+        <v>-6.36</v>
       </c>
       <c r="L47" t="n">
-        <v>3.26</v>
+        <v>6.51</v>
       </c>
       <c r="M47" t="n">
         <v>0.6</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>9.73</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45615.55208333334</v>
+        <v>45617.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>515.05</v>
+        <v>496.05</v>
       </c>
       <c r="I48" t="n">
         <v>498.6155991367642</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.11</v>
+        <v>-9.57</v>
       </c>
       <c r="L48" t="n">
-        <v>9.67</v>
+        <v>14.5</v>
       </c>
       <c r="M48" t="n">
         <v>0.44</v>
       </c>
       <c r="N48" t="n">
-        <v>2.91</v>
+        <v>4.67</v>
       </c>
       <c r="O48" t="n">
         <v>4.71</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45629.38541666666</v>
+        <v>45629.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>536.7</v>
+        <v>539.5</v>
       </c>
       <c r="I49" t="n">
         <v>538.8325956448328</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-8.19</v>
+        <v>-8.76</v>
       </c>
       <c r="L49" t="n">
-        <v>8.94</v>
+        <v>9.57</v>
       </c>
       <c r="M49" t="n">
         <v>4.23</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.18</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>549.2</v>
+        <v>536.7</v>
       </c>
       <c r="I50" t="n">
         <v>546.4380106712905</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>1.8</v>
+        <v>-0.52</v>
       </c>
       <c r="L50" t="n">
-        <v>0.58</v>
+        <v>1.34</v>
       </c>
       <c r="M50" t="n">
         <v>0.37</v>
       </c>
       <c r="N50" t="n">
-        <v>1.67</v>
+        <v>2.19</v>
       </c>
       <c r="O50" t="n">
         <v>1.6</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.05</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>519.85</v>
+        <v>540.2</v>
       </c>
       <c r="I51" t="n">
         <v>527.5386300603103</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>3.14</v>
+        <v>-0.65</v>
       </c>
       <c r="L51" t="n">
         <v>2.57</v>
@@ -3348,7 +3959,7 @@
         <v>1.52</v>
       </c>
       <c r="N51" t="n">
-        <v>2.93</v>
+        <v>3.46</v>
       </c>
       <c r="O51" t="n">
         <v>-2.19</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>7.53</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>515</v>
+        <v>498.3</v>
       </c>
       <c r="I52" t="n">
         <v>510.5442746119662</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.66</v>
+        <v>-7.76</v>
       </c>
       <c r="L52" t="n">
-        <v>6.12</v>
+        <v>7.84</v>
       </c>
       <c r="M52" t="n">
         <v>-0</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>482.1</v>
+        <v>492.9</v>
       </c>
       <c r="I53" t="n">
         <v>491.2511227590605</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K53" t="n">
-        <v>3.25</v>
+        <v>1.08</v>
       </c>
       <c r="L53" t="n">
         <v>3.91</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.83</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45680.55208333334</v>
+        <v>45681.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>463.85</v>
+        <v>451.9</v>
       </c>
       <c r="I54" t="n">
         <v>457.2393882232422</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.89</v>
+        <v>-8.32</v>
       </c>
       <c r="L54" t="n">
-        <v>8.050000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="M54" t="n">
         <v>0.03</v>
       </c>
       <c r="N54" t="n">
-        <v>2.96</v>
+        <v>3.71</v>
       </c>
       <c r="O54" t="n">
         <v>1.5</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.41</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>386.5</v>
+        <v>401.6</v>
       </c>
       <c r="I55" t="n">
         <v>390.4020533329181</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K55" t="n">
-        <v>14.47</v>
+        <v>11.13</v>
       </c>
       <c r="L55" t="n">
         <v>3.18</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>428</v>
+        <v>418.25</v>
       </c>
       <c r="I56" t="n">
         <v>420.1283342652284</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K56" t="n">
-        <v>6.57</v>
+        <v>4.15</v>
       </c>
       <c r="L56" t="n">
         <v>4.38</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.26</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>401.4</v>
+        <v>417</v>
       </c>
       <c r="I57" t="n">
         <v>412.928395873482</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K57" t="n">
-        <v>4.03</v>
+        <v>0.3</v>
       </c>
       <c r="L57" t="n">
         <v>3.37</v>
@@ -3690,7 +4373,7 @@
         <v>3.94</v>
       </c>
       <c r="N57" t="n">
-        <v>3.03</v>
+        <v>5.53</v>
       </c>
       <c r="O57" t="n">
         <v>-2.39</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>422.85</v>
+        <v>410</v>
       </c>
       <c r="I58" t="n">
         <v>414.8901843242985</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K58" t="n">
-        <v>1.4</v>
+        <v>-1.68</v>
       </c>
       <c r="L58" t="n">
         <v>2.29</v>
@@ -3747,7 +4442,7 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>4.49</v>
       </c>
       <c r="O58" t="n">
         <v>5.53</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>8.83</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>414.95</v>
+        <v>427.5</v>
       </c>
       <c r="I59" t="n">
         <v>415.9664952085391</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.21</v>
+        <v>-4.27</v>
       </c>
       <c r="L59" t="n">
-        <v>3.59</v>
+        <v>4.56</v>
       </c>
       <c r="M59" t="n">
         <v>4.39</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>6.24</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>409.3</v>
+        <v>404.9</v>
       </c>
       <c r="I60" t="n">
         <v>405.9228322826735</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.26</v>
+        <v>-5.29</v>
       </c>
       <c r="L60" t="n">
-        <v>4.4</v>
+        <v>5.63</v>
       </c>
       <c r="M60" t="n">
         <v>0.13</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.58</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45834.38541666666</v>
+        <v>45834.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="I61" t="n">
         <v>403.8570868099816</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K61" t="n">
-        <v>1.21</v>
+        <v>0.22</v>
       </c>
       <c r="L61" t="n">
         <v>1.14</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>395</v>
+        <v>390.15</v>
       </c>
       <c r="I62" t="n">
         <v>390.6101208113786</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.23</v>
+        <v>-3.43</v>
       </c>
       <c r="L62" t="n">
-        <v>3.42</v>
+        <v>4.65</v>
       </c>
       <c r="M62" t="n">
         <v>1</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.09</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45901.55208333334</v>
+        <v>45902.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>361.6</v>
+        <v>367.85</v>
       </c>
       <c r="I63" t="n">
         <v>364.4868805098743</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K63" t="n">
-        <v>7.32</v>
+        <v>5.72</v>
       </c>
       <c r="L63" t="n">
         <v>1.96</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.18</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45925.38541666666</v>
+        <v>45925.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>379.25</v>
+        <v>375</v>
       </c>
       <c r="I64" t="n">
         <v>375.5251013602234</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>3.1</v>
+        <v>1.94</v>
       </c>
       <c r="L64" t="n">
         <v>2.09</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>3.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45933.38541666666</v>
+        <v>45933.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>378.35</v>
+        <v>380.5</v>
       </c>
       <c r="I65" t="n">
         <v>379.6899507580215</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.89</v>
+        <v>-1.47</v>
       </c>
       <c r="L65" t="n">
         <v>4.08</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>4.5</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>370.95</v>
+        <v>364.85</v>
       </c>
       <c r="I66" t="n">
         <v>367.9667930383577</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>32</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.51</v>
+        <v>-4.11</v>
       </c>
       <c r="L66" t="n">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="M66" t="n">
         <v>0.47</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.59</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45987.55208333334</v>
+        <v>45988.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>356.3</v>
+        <v>363.1</v>
       </c>
       <c r="I67" t="n">
         <v>361.8621745429037</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K67" t="n">
-        <v>2.34</v>
+        <v>0.48</v>
       </c>
       <c r="L67" t="n">
         <v>2.15</v>
@@ -4260,7 +5063,7 @@
         <v>0.42</v>
       </c>
       <c r="N67" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="O67" t="n">
         <v>-2.2</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.35</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>353.9</v>
+        <v>344</v>
       </c>
       <c r="I68" t="n">
         <v>350.6190697824009</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.53</v>
+        <v>-5.26</v>
       </c>
       <c r="L68" t="n">
-        <v>4.1</v>
+        <v>5.51</v>
       </c>
       <c r="M68" t="n">
         <v>0.36</v>
       </c>
       <c r="N68" t="n">
-        <v>1.93</v>
+        <v>3.38</v>
       </c>
       <c r="O68" t="n">
         <v>1.75</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>5.37</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>343.3</v>
+        <v>356.5</v>
       </c>
       <c r="I69" t="n">
         <v>346.2326963473008</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K69" t="n">
-        <v>0.2</v>
+        <v>-3.63</v>
       </c>
       <c r="L69" t="n">
-        <v>2.86</v>
+        <v>3.92</v>
       </c>
       <c r="M69" t="n">
         <v>0.73</v>
       </c>
       <c r="N69" t="n">
-        <v>1.19</v>
+        <v>3.12</v>
       </c>
       <c r="O69" t="n">
         <v>-3.38</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.02</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>367.35</v>
+        <v>363.6</v>
       </c>
       <c r="I70" t="n">
         <v>366.4664759459833</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>3.04</v>
+        <v>1.99</v>
       </c>
       <c r="L70" t="n">
         <v>3.69</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>6.16</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46050.38541666666</v>
+        <v>46050.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>373.5</v>
+        <v>377.4</v>
       </c>
       <c r="I71" t="n">
         <v>374.114668969127</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K71" t="n">
-        <v>-2.72</v>
+        <v>-3.8</v>
       </c>
       <c r="L71" t="n">
-        <v>3.82</v>
+        <v>4.08</v>
       </c>
       <c r="M71" t="n">
         <v>1.15</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>5.92</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46054.38541666666</v>
+        <v>46054.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>371.15</v>
+        <v>358.7</v>
       </c>
       <c r="I72" t="n">
         <v>358.8860099970077</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.66</v>
+        <v>-4.95</v>
       </c>
       <c r="L72" t="n">
         <v>7.07</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.17</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H73" t="n">
-        <v>346.2</v>
+        <v>348.4</v>
       </c>
       <c r="I73" t="n">
         <v>347.2498280990849</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>44.83333333333334</v>
+        <v>45</v>
       </c>
       <c r="K73" t="n">
-        <v>3.48</v>
+        <v>2.87</v>
       </c>
       <c r="L73" t="n">
         <v>7.75</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>6.44</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>329.9</v>
+        <v>313.35</v>
       </c>
       <c r="I74" t="n">
         <v>325.9567873975241</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.31</v>
+        <v>-10.06</v>
       </c>
       <c r="L74" t="n">
-        <v>5.5</v>
+        <v>10.86</v>
       </c>
       <c r="M74" t="n">
         <v>1.55</v>
       </c>
       <c r="N74" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="O74" t="n">
         <v>2.83</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>10.06</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>329.7</v>
+        <v>341.5</v>
       </c>
       <c r="I75" t="n">
         <v>331.095244571328</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.22</v>
+        <v>-8.98</v>
       </c>
       <c r="L75" t="n">
-        <v>5.51</v>
+        <v>10.05</v>
       </c>
       <c r="M75" t="n">
         <v>4.77</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.96</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46141.38541666666</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>365</v>
+        <v>362.3</v>
       </c>
       <c r="I76" t="n">
         <v>362.7469713425655</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K76" t="n">
-        <v>6.88</v>
+        <v>6.09</v>
       </c>
       <c r="L76" t="n">
         <v>1.14</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>6.87</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>335.75</v>
+        <v>341</v>
       </c>
       <c r="I77" t="n">
         <v>339.1291331155288</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K77" t="n">
-        <v>7.33</v>
+        <v>5.88</v>
       </c>
       <c r="L77" t="n">
         <v>1.38</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>4.83</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H78" t="n">
-        <v>357.35</v>
+        <v>347.5</v>
       </c>
       <c r="I78" t="n">
         <v>355.5884819263562</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K78" t="n">
-        <v>4.79</v>
+        <v>1.91</v>
       </c>
       <c r="L78" t="n">
         <v>1.55</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>6.01</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>361</v>
+        <v>366.65</v>
       </c>
       <c r="I79" t="n">
         <v>363.4649229254892</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K79" t="n">
-        <v>-3.88</v>
+        <v>-5.51</v>
       </c>
       <c r="L79" t="n">
-        <v>4.95</v>
+        <v>5.84</v>
       </c>
       <c r="M79" t="n">
         <v>0.48</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>5.88</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46241.55208333334</v>
+        <v>46244.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>366.4</v>
+        <v>344.5</v>
       </c>
       <c r="I80" t="n">
         <v>359.0983477426768</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-6.04</v>
       </c>
       <c r="L80" t="n">
-        <v>2.66</v>
+        <v>6.07</v>
       </c>
       <c r="M80" t="n">
         <v>0.97</v>
       </c>
       <c r="N80" t="n">
-        <v>1.25</v>
+        <v>6.45</v>
       </c>
       <c r="O80" t="n">
         <v>2.01</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H81" t="n">
-        <v>304.05</v>
+        <v>306.85</v>
       </c>
       <c r="I81" t="n">
         <v>304.616213832209</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>64</v>
+        <v>64.16666666666667</v>
       </c>
       <c r="K81" t="n">
-        <v>11.74</v>
+        <v>10.93</v>
       </c>
       <c r="L81" t="n">
         <v>6.33</v>
@@ -5067,7 +6038,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>5.07</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>301.8</v>
+        <v>291.85</v>
       </c>
       <c r="I82" t="n">
         <v>297.4141401809867</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K82" t="n">
-        <v>-1.65</v>
+        <v>-4.89</v>
       </c>
       <c r="L82" t="n">
-        <v>3.7</v>
+        <v>5.08</v>
       </c>
       <c r="M82" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="N82" t="n">
-        <v>1.69</v>
+        <v>2.97</v>
       </c>
       <c r="O82" t="n">
         <v>1.1</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,12 @@
       <c r="Q83" t="n">
         <v>6</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7277,7 +8278,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.3</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="6">
@@ -7287,7 +8288,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="7">
@@ -7297,7 +8298,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="8">
@@ -7307,7 +8308,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7317,7 +8318,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -7327,7 +8328,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -7367,7 +8368,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.66</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="15">
@@ -7377,7 +8378,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.87</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="16">
@@ -7387,7 +8388,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="17">
@@ -7397,7 +8398,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54.43</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="18">
@@ -7407,7 +8408,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.1</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="19">
@@ -7417,7 +8418,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="20">
@@ -7427,7 +8428,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="21">
@@ -7437,7 +8438,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.4</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="22">
@@ -7447,7 +8448,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
@@ -7457,7 +8458,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -7467,7 +8468,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="25">
@@ -7477,7 +8478,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.86</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="26">
@@ -7487,7 +8488,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.22</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="27">
@@ -7497,7 +8498,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.75</v>
+        <v>24.19</v>
       </c>
     </row>
     <row r="28">
@@ -7507,7 +8508,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
